--- a/new12.xlsx
+++ b/new12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,12 +515,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prepare test data with active and inactive members across multiple Trading Partner IDs and Group System Keys, including at least one active member matching the runtime configuration values.</t>
+          <t>Configure runtime parameters with a valid target Trading Partner ID and a valid specific Group System Key.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Test data exists with clear coverage for matching and non-matching combinations.</t>
+          <t>Runtime configuration is saved successfully and available to the outbound extraction process.</t>
         </is>
       </c>
     </row>
@@ -547,12 +547,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Set runtime configuration parameters with the target Trading Partner ID and specific Group System Key.</t>
+          <t>Prepare source data containing active and inactive members across multiple Trading Partner IDs and Group System Keys.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Runtime configuration is saved with the intended parameter values.</t>
+          <t>Test data exists with clear differentiation by member status, Trading Partner ID, and Group System Key.</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Execute the outbound data extraction process.</t>
+          <t>Execute the outbound data extraction query.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Extraction process starts successfully without configuration errors.</t>
+          <t>Extraction process completes successfully without runtime errors.</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Review the extracted dataset or generated outbound file contents.</t>
+          <t>Review the extracted dataset for members matching the configured Trading Partner ID and Group System Key.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Only active members matching both the configured Trading Partner ID and Group System Key are included.</t>
+          <t>Only records with the configured Trading Partner ID and configured Group System Key are present in the extracted dataset.</t>
         </is>
       </c>
     </row>
@@ -633,22 +633,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TS_002: Verify inactive members are excluded even when Trading Partner ID and Group System Key match</t>
+          <t>TS_001: Verify extraction includes only active members for configured Trading Partner ID and Group System Key</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prepare test data containing inactive members with the same Trading Partner ID and Group System Key as the runtime configuration.</t>
+          <t>Validate the status of all extracted members.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Inactive matching records are available for validation.</t>
+          <t>All extracted members are active; no inactive member records are included.</t>
         </is>
       </c>
     </row>
@@ -665,22 +665,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TS_002: Verify inactive members are excluded even when Trading Partner ID and Group System Key match</t>
+          <t>TS_002: Verify extraction excludes inactive members even when Trading Partner ID and Group System Key match</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Set runtime configuration parameters to the Trading Partner ID and Group System Key used by the inactive test records.</t>
+          <t>Configure runtime parameters with a valid target Trading Partner ID and a valid specific Group System Key.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Runtime configuration is saved correctly.</t>
+          <t>Runtime configuration is saved successfully and available to the outbound extraction process.</t>
         </is>
       </c>
     </row>
@@ -697,22 +697,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TS_002: Verify inactive members are excluded even when Trading Partner ID and Group System Key match</t>
+          <t>TS_002: Verify extraction excludes inactive members even when Trading Partner ID and Group System Key match</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Run the outbound data extraction process.</t>
+          <t>Prepare source data containing inactive members that match the configured Trading Partner ID and Group System Key.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Extraction completes successfully.</t>
+          <t>Inactive matching records are available in the source dataset.</t>
         </is>
       </c>
     </row>
@@ -729,22 +729,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TS_002: Verify inactive members are excluded even when Trading Partner ID and Group System Key match</t>
+          <t>TS_002: Verify extraction excludes inactive members even when Trading Partner ID and Group System Key match</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Inspect the extracted output for the inactive matching members.</t>
+          <t>Execute the outbound data extraction query.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inactive members are not present in the extracted output.</t>
+          <t>Extraction process completes successfully without runtime errors.</t>
         </is>
       </c>
     </row>
@@ -761,22 +761,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TS_003: Verify active members are excluded when Trading Partner ID does not match runtime configuration</t>
+          <t>TS_002: Verify extraction excludes inactive members even when Trading Partner ID and Group System Key match</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prepare test data containing active members with the correct Group System Key but a different Trading Partner ID from the runtime configuration.</t>
+          <t>Search the extracted dataset for the inactive matching members.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Active non-matching Trading Partner records are available.</t>
+          <t>Inactive members are not present in the extracted dataset.</t>
         </is>
       </c>
     </row>
@@ -793,22 +793,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TS_003: Verify active members are excluded when Trading Partner ID does not match runtime configuration</t>
+          <t>TS_003: Verify extraction excludes active members with non-matching Trading Partner ID</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Set runtime configuration parameters with the target Trading Partner ID and corresponding Group System Key.</t>
+          <t>Configure runtime parameters with a target Trading Partner ID and a specific Group System Key.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Runtime configuration is saved correctly.</t>
+          <t>Runtime configuration is saved successfully and available to the outbound extraction process.</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TS_003: Verify active members are excluded when Trading Partner ID does not match runtime configuration</t>
+          <t>TS_003: Verify extraction excludes active members with non-matching Trading Partner ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Execute the outbound data extraction process.</t>
+          <t>Prepare source data containing active members with the configured Group System Key but a different Trading Partner ID.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Extraction completes successfully.</t>
+          <t>Active non-matching Trading Partner ID records are available in the source dataset.</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TS_003: Verify active members are excluded when Trading Partner ID does not match runtime configuration</t>
+          <t>TS_003: Verify extraction excludes active members with non-matching Trading Partner ID</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Review the extracted output for active members with non-matching Trading Partner IDs.</t>
+          <t>Execute the outbound data extraction query.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Active members with non-matching Trading Partner IDs are excluded from the output.</t>
+          <t>Extraction process completes successfully without runtime errors.</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TS_004: Verify active members are excluded when Group System Key does not match runtime configuration</t>
+          <t>TS_003: Verify extraction excludes active members with non-matching Trading Partner ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prepare test data containing active members with the correct Trading Partner ID but a different Group System Key from the runtime configuration.</t>
+          <t>Review the extracted dataset for members with non-matching Trading Partner IDs.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Active non-matching Group System Key records are available.</t>
+          <t>Active members with Trading Partner IDs different from the configured value are excluded from the extracted dataset.</t>
         </is>
       </c>
     </row>
@@ -921,22 +921,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TS_004: Verify active members are excluded when Group System Key does not match runtime configuration</t>
+          <t>TS_004: Verify extraction excludes active members with non-matching Group System Key</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Set runtime configuration parameters with the target Trading Partner ID and target Group System Key.</t>
+          <t>Configure runtime parameters with a target Trading Partner ID and a specific Group System Key.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Runtime configuration is saved correctly.</t>
+          <t>Runtime configuration is saved successfully and available to the outbound extraction process.</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TS_004: Verify active members are excluded when Group System Key does not match runtime configuration</t>
+          <t>TS_004: Verify extraction excludes active members with non-matching Group System Key</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Run the outbound data extraction process.</t>
+          <t>Prepare source data containing active members with the configured Trading Partner ID but a different Group System Key.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Extraction completes successfully.</t>
+          <t>Active non-matching Group System Key records are available in the source dataset.</t>
         </is>
       </c>
     </row>
@@ -985,22 +985,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TS_004: Verify active members are excluded when Group System Key does not match runtime configuration</t>
+          <t>TS_004: Verify extraction excludes active members with non-matching Group System Key</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inspect the extracted output for active members with non-matching Group System Keys.</t>
+          <t>Execute the outbound data extraction query.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Active members with non-matching Group System Keys are excluded from the output.</t>
+          <t>Extraction process completes successfully without runtime errors.</t>
         </is>
       </c>
     </row>
@@ -1017,22 +1017,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TS_005: Verify extraction returns all eligible active members when multiple records match both runtime parameters</t>
+          <t>TS_004: Verify extraction excludes active members with non-matching Group System Key</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prepare multiple active member records that all share the configured Trading Partner ID and Group System Key.</t>
+          <t>Review the extracted dataset for members with non-matching Group System Keys.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Multiple eligible matching records are available.</t>
+          <t>Active members with Group System Keys different from the configured value are excluded from the extracted dataset.</t>
         </is>
       </c>
     </row>
@@ -1049,22 +1049,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TS_005: Verify extraction returns all eligible active members when multiple records match both runtime parameters</t>
+          <t>TS_005: Verify extraction returns only records matching both configured filters simultaneously</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Configure the runtime parameters with the shared Trading Partner ID and Group System Key used by the eligible records.</t>
+          <t>Configure runtime parameters with a target Trading Partner ID and a specific Group System Key.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Runtime configuration is saved correctly.</t>
+          <t>Runtime configuration is saved successfully and available to the outbound extraction process.</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TS_005: Verify extraction returns all eligible active members when multiple records match both runtime parameters</t>
+          <t>TS_005: Verify extraction returns only records matching both configured filters simultaneously</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Execute the outbound data extraction process.</t>
+          <t>Prepare source data containing active members where some match only Trading Partner ID, some match only Group System Key, and some match both.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Extraction completes successfully.</t>
+          <t>Source data supports validation of combined filter behavior.</t>
         </is>
       </c>
     </row>
@@ -1113,22 +1113,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TS_005: Verify extraction returns all eligible active members when multiple records match both runtime parameters</t>
+          <t>TS_005: Verify extraction returns only records matching both configured filters simultaneously</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Compare the extracted output against the prepared eligible records.</t>
+          <t>Execute the outbound data extraction query.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>All active records matching both runtime parameters are included with no eligible omissions.</t>
+          <t>Extraction process completes successfully without runtime errors.</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TS_006: Verify records with completely blank Member ID are rejected during file generation</t>
+          <t>TS_005: Verify extraction returns only records matching both configured filters simultaneously</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prepare an extracted eligible record with all required data except a completely blank Member ID.</t>
+          <t>Compare extracted records against the source dataset.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Test record is available with blank Member ID and otherwise valid data.</t>
+          <t>Only active members matching both the configured Trading Partner ID and configured Group System Key are included; partial matches are excluded.</t>
         </is>
       </c>
     </row>
@@ -1177,22 +1177,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TS_006: Verify records with completely blank Member ID are rejected during file generation</t>
+          <t>TS_006: Verify records with blank Member ID are rejected during file generation</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trigger the file generation engine using the prepared dataset.</t>
+          <t>Prepare extracted eligible records including at least one record with a completely blank Member ID and otherwise valid data.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>File generation process starts successfully.</t>
+          <t>Test data includes a record with blank Member ID and valid comparison records.</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1209,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TS_006: Verify records with completely blank Member ID are rejected during file generation</t>
+          <t>TS_006: Verify records with blank Member ID are rejected during file generation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Review the generated output and processing results for the record with blank Member ID.</t>
+          <t>Start the outbound file generation engine using the prepared extracted dataset.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>The record with completely blank Member ID is rejected and not written to the outbound file.</t>
+          <t>File generation process starts successfully.</t>
         </is>
       </c>
     </row>
@@ -1241,22 +1241,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TS_006: Verify records with completely blank Member ID are rejected during file generation</t>
+          <t>TS_006: Verify records with blank Member ID are rejected during file generation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Check system validation or rejection logs for the rejected record.</t>
+          <t>Review the generated outbound content and processing results for the blank Member ID record.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A rejection entry is recorded indicating missing crucial demographic data for Member ID.</t>
+          <t>The record with completely blank Member ID is rejected and not written to the outbound file.</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TS_007: Verify records with unformatted Date of Birth are rejected during file generation</t>
+          <t>TS_006: Verify records with blank Member ID are rejected during file generation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prepare an extracted eligible record with a populated Member ID and an unformatted Date of Birth value.</t>
+          <t>Review rejection details or processing logs for the excluded record.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Test record is available with invalid Date of Birth format and otherwise valid data.</t>
+          <t>Rejection is recorded with an error or validation reason indicating missing crucial demographic data or blank Member ID.</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Execute the file generation engine using the prepared dataset.</t>
+          <t>Prepare extracted eligible records including at least one record with an unformatted Date of Birth and otherwise valid data.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>File generation process starts successfully.</t>
+          <t>Test data includes a record with invalid Date of Birth format and valid comparison records.</t>
         </is>
       </c>
     </row>
@@ -1342,17 +1342,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inspect the generated output and processing results for the record with unformatted Date of Birth.</t>
+          <t>Start the outbound file generation engine using the prepared extracted dataset.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>The record with unformatted Date of Birth is rejected and excluded from the outbound file.</t>
+          <t>File generation process starts successfully.</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Review validation or rejection logs for the rejected record.</t>
+          <t>Review the generated outbound content and processing results for the invalid Date of Birth record.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A rejection entry is recorded indicating invalid or unformatted Date of Birth.</t>
+          <t>The record with unformatted Date of Birth is rejected and not written to the outbound file.</t>
         </is>
       </c>
     </row>
@@ -1401,22 +1401,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TS_008: Verify valid records are accepted when crucial demographic data is present and correctly formatted</t>
+          <t>TS_007: Verify records with unformatted Date of Birth are rejected during file generation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Prepare an extracted eligible record with a populated Member ID and correctly formatted Date of Birth along with all other required demographic data.</t>
+          <t>Review rejection details or processing logs for the excluded record.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Test record is available with valid crucial demographic data.</t>
+          <t>Rejection is recorded with an error or validation reason indicating invalid or unformatted Date of Birth.</t>
         </is>
       </c>
     </row>
@@ -1433,22 +1433,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TS_008: Verify valid records are accepted when crucial demographic data is present and correctly formatted</t>
+          <t>TS_008: Verify valid records are accepted when crucial demographic data is present and properly formatted</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Run the file generation engine using the prepared valid dataset.</t>
+          <t>Prepare extracted eligible records with populated Member ID and properly formatted Date of Birth values.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>File generation process completes successfully.</t>
+          <t>Test data includes records that satisfy demographic validation rules.</t>
         </is>
       </c>
     </row>
@@ -1465,22 +1465,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TS_008: Verify valid records are accepted when crucial demographic data is present and correctly formatted</t>
+          <t>TS_008: Verify valid records are accepted when crucial demographic data is present and properly formatted</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Review the generated outbound file for the valid record.</t>
+          <t>Start the outbound file generation engine using the prepared extracted dataset.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The valid record is included in the outbound file without rejection.</t>
+          <t>File generation process starts successfully.</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TS_009: Verify mixed valid and invalid records result in selective rejection only for invalid records</t>
+          <t>TS_008: Verify valid records are accepted when crucial demographic data is present and properly formatted</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Prepare a dataset containing one valid record, one record with blank Member ID, and one record with unformatted Date of Birth.</t>
+          <t>Review the generated outbound file content for the valid records.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mixed dataset is available with both valid and invalid records.</t>
+          <t>Valid records are included in the outbound file without rejection.</t>
         </is>
       </c>
     </row>
@@ -1534,17 +1534,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Execute the file generation engine using the mixed dataset.</t>
+          <t>Prepare extracted eligible records containing valid records, records with blank Member ID, and records with unformatted Date of Birth.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>File generation process completes without aborting the entire batch.</t>
+          <t>Mixed test data is available for selective validation testing.</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Inspect the generated outbound file contents.</t>
+          <t>Start the outbound file generation engine using the mixed dataset.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Only the valid record is included in the outbound file.</t>
+          <t>File generation process starts successfully.</t>
         </is>
       </c>
     </row>
@@ -1598,17 +1598,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Review rejection logs for the invalid records.</t>
+          <t>Review the generated outbound file content.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Each invalid record is rejected with the appropriate validation reason.</t>
+          <t>Only valid records are written to the outbound file; records with blank Member ID or unformatted Date of Birth are excluded.</t>
         </is>
       </c>
     </row>
@@ -1625,22 +1625,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TS_010: Verify outbound file is generated with required prefix and extension</t>
+          <t>TS_009: Verify mixed valid and invalid records result in selective rejection only for invalid records</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Prepare a valid eligible dataset that passes extraction and file generation validations.</t>
+          <t>Review processing logs or rejection output.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valid dataset is available for successful file creation.</t>
+          <t>Each invalid record is individually rejected with the appropriate validation reason; valid records are not incorrectly rejected.</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TS_010: Verify outbound file is generated with required prefix and extension</t>
+          <t>TS_010: Verify outbound file is generated successfully with required naming convention</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Execute the outbound file generation process.</t>
+          <t>Prepare a valid extracted dataset eligible for outbound file generation.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>File generation completes successfully.</t>
+          <t>Valid input data is available for successful file creation.</t>
         </is>
       </c>
     </row>
@@ -1689,22 +1689,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TS_010: Verify outbound file is generated with required prefix and extension</t>
+          <t>TS_010: Verify outbound file is generated successfully with required naming convention</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Locate the generated outbound file in the target output location.</t>
+          <t>Start the outbound file generation engine.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>A text file is created in the expected output location.</t>
+          <t>File generation completes successfully and creates an outbound text file.</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1721,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TS_010: Verify outbound file is generated with required prefix and extension</t>
+          <t>TS_010: Verify outbound file is generated successfully with required naming convention</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Validate the generated file name against the pattern OUTBOUND_ELIG_EFF_[Timestamp]_[TrackingID].txt.</t>
+          <t>Capture the generated file name from the output location.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>File name begins with OUTBOUND_ELIG_EFF_, contains a timestamp segment, contains a tracking ID segment, and ends with .txt.</t>
+          <t>A single outbound text file is present in the expected output location.</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1753,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TS_011: Verify generated file name contains a populated timestamp value</t>
+          <t>TS_010: Verify outbound file is generated successfully with required naming convention</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Prepare a valid eligible dataset for outbound processing.</t>
+          <t>Compare the generated file name against the required pattern OUTBOUND_ELIG_EFF_[Timestamp]_[TrackingID].txt.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valid dataset is available.</t>
+          <t>File name matches the required structural naming convention exactly, including prefix, timestamp segment, tracking ID segment, and .txt extension.</t>
         </is>
       </c>
     </row>
@@ -1785,22 +1785,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TS_011: Verify generated file name contains a populated timestamp value</t>
+          <t>TS_011: Verify generated file name contains a populated timestamp segment</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Run the outbound file generation process and capture the system time at execution.</t>
+          <t>Prepare a valid extracted dataset eligible for outbound file generation.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>File generation completes successfully and execution time is known.</t>
+          <t>Valid input data is available for successful file creation.</t>
         </is>
       </c>
     </row>
@@ -1817,22 +1817,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TS_011: Verify generated file name contains a populated timestamp value</t>
+          <t>TS_011: Verify generated file name contains a populated timestamp segment</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inspect the generated file name and isolate the timestamp segment.</t>
+          <t>Start the outbound file generation engine.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Timestamp segment is present and not blank.</t>
+          <t>File generation completes successfully and creates an outbound text file.</t>
         </is>
       </c>
     </row>
@@ -1849,22 +1849,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TS_011: Verify generated file name contains a populated timestamp value</t>
+          <t>TS_011: Verify generated file name contains a populated timestamp segment</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Compare the timestamp segment format to the system-defined standard.</t>
+          <t>Inspect the timestamp portion of the generated file name between OUTBOUND_ELIG_EFF_ and the tracking ID segment.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Timestamp value is formatted per the standard and aligns with the execution window.</t>
+          <t>Timestamp segment is present, populated, and not blank.</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TS_012: Verify generated file name contains a populated tracking ID value</t>
+          <t>TS_012: Verify generated file name contains a populated tracking ID segment</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prepare a valid eligible dataset for outbound processing.</t>
+          <t>Prepare a valid extracted dataset eligible for outbound file generation.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Valid dataset is available.</t>
+          <t>Valid input data is available for successful file creation.</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TS_012: Verify generated file name contains a populated tracking ID value</t>
+          <t>TS_012: Verify generated file name contains a populated tracking ID segment</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Execute the outbound file generation process.</t>
+          <t>Start the outbound file generation engine.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>File generation completes successfully.</t>
+          <t>File generation completes successfully and creates an outbound text file.</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TS_012: Verify generated file name contains a populated tracking ID value</t>
+          <t>TS_012: Verify generated file name contains a populated tracking ID segment</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Inspect the generated file name and isolate the tracking ID segment.</t>
+          <t>Inspect the tracking ID portion of the generated file name between the timestamp segment and the .txt extension.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tracking ID segment is present and not blank.</t>
+          <t>Tracking ID segment is present, populated, and not blank.</t>
         </is>
       </c>
     </row>
@@ -1977,22 +1977,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TS_012: Verify generated file name contains a populated tracking ID value</t>
+          <t>TS_013: Verify generated outbound file uses .txt extension</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cross-check the tracking ID segment with the system-generated transmission or batch tracking identifier.</t>
+          <t>Prepare a valid extracted dataset eligible for outbound file generation.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tracking ID in the file name matches the associated system tracking identifier.</t>
+          <t>Valid input data is available for successful file creation.</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TS_013: Verify local staging status changes from Ready to Processed after successful file creation</t>
+          <t>TS_013: Verify generated outbound file uses .txt extension</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prepare a staging record in Ready status linked to valid outbound data eligible for file creation.</t>
+          <t>Start the outbound file generation engine.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Staging record exists in Ready status before processing.</t>
+          <t>File generation completes successfully and creates an outbound file.</t>
         </is>
       </c>
     </row>
@@ -2041,22 +2041,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TS_013: Verify local staging status changes from Ready to Processed after successful file creation</t>
+          <t>TS_013: Verify generated outbound file uses .txt extension</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Execute the outbound file creation process for the staging record.</t>
+          <t>Inspect the generated file name extension.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>File is created successfully for the staging record.</t>
+          <t>Generated outbound file ends with the .txt extension.</t>
         </is>
       </c>
     </row>
@@ -2073,22 +2073,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TS_013: Verify local staging status changes from Ready to Processed after successful file creation</t>
+          <t>TS_014: Verify staging record status changes from Ready to Processed after successful file creation</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Query or review the local staging record immediately after successful file creation.</t>
+          <t>Prepare a staging record with status set to Ready and associate it with valid outbound data eligible for file creation.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Staging record status changes from Ready to Processed immediately after file creation.</t>
+          <t>Staging record exists in Ready status before processing begins.</t>
         </is>
       </c>
     </row>
@@ -2105,22 +2105,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TS_014: Verify status transition occurs only after successful file creation</t>
+          <t>TS_014: Verify staging record status changes from Ready to Processed after successful file creation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Prepare a staging record in Ready status with valid outbound data.</t>
+          <t>Start the outbound file generation process for the staging record.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Staging record exists in Ready status before processing.</t>
+          <t>File generation completes successfully and creates the outbound file.</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TS_014: Verify status transition occurs only after successful file creation</t>
+          <t>TS_014: Verify staging record status changes from Ready to Processed after successful file creation</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Start the outbound process and monitor file creation completion event and staging status updates.</t>
+          <t>Query or review the staging record immediately after successful file creation.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Processing events can be observed in sequence.</t>
+          <t>Staging record status is updated from Ready to Processed.</t>
         </is>
       </c>
     </row>
@@ -2169,22 +2169,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TS_014: Verify status transition occurs only after successful file creation</t>
+          <t>TS_015: Verify status transition occurs immediately upon successful file creation</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Verify the staging status at the point before file creation completes and again after completion.</t>
+          <t>Prepare a staging record with status set to Ready and associate it with valid outbound data eligible for file creation.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Status remains Ready before successful file creation and changes to Processed only after successful file creation completes.</t>
+          <t>Staging record exists in Ready status before processing begins.</t>
         </is>
       </c>
     </row>
@@ -2201,22 +2201,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TS_015: Verify staging status does not remain Ready after successful file creation</t>
+          <t>TS_015: Verify status transition occurs immediately upon successful file creation</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Prepare a valid staging record in Ready status for outbound processing.</t>
+          <t>Start the outbound file generation process and capture the file creation completion time.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Staging record is available in Ready status.</t>
+          <t>Successful file creation time is available for comparison.</t>
         </is>
       </c>
     </row>
@@ -2233,22 +2233,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TS_015: Verify staging status does not remain Ready after successful file creation</t>
+          <t>TS_015: Verify status transition occurs immediately upon successful file creation</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Execute the outbound file creation process to completion.</t>
+          <t>Query the staging record status as soon as file creation completes.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>File creation completes successfully.</t>
+          <t>Staging record reflects Processed status immediately after successful file creation with no intermediate lingering Ready state.</t>
         </is>
       </c>
     </row>
@@ -2265,22 +2265,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TS_015: Verify staging status does not remain Ready after successful file creation</t>
+          <t>TS_016: Verify only Ready staging records are transitioned as part of successful processing</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Review the staging record status after processing completes.</t>
+          <t>Prepare one staging record in Ready status with valid outbound data and separate records in other statuses.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Staging record no longer shows Ready and is updated to Processed.</t>
+          <t>Test data includes staging records in Ready and non-Ready statuses.</t>
         </is>
       </c>
     </row>
@@ -2297,22 +2297,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TS_016: Verify end-to-end processing from extraction through file creation and status update</t>
+          <t>TS_016: Verify only Ready staging records are transitioned as part of successful processing</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Prepare active member data matching the configured Trading Partner ID and Group System Key with valid crucial demographic data and create a linked staging record in Ready status.</t>
+          <t>Start the outbound file generation process for the eligible Ready staging record.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>End-to-end test data is available and staging record starts in Ready status.</t>
+          <t>File generation completes successfully for the eligible Ready staging record.</t>
         </is>
       </c>
     </row>
@@ -2329,118 +2329,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TS_016: Verify end-to-end processing from extraction through file creation and status update</t>
+          <t>TS_016: Verify only Ready staging records are transitioned as part of successful processing</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Set runtime configuration parameters with the target Trading Partner ID and Group System Key.</t>
+          <t>Review statuses of all staging records after processing.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Runtime configuration is saved correctly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>US_2045</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Outbound Member Eligibility Reporting</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>TS_016: Verify end-to-end processing from extraction through file creation and status update</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Execute the full outbound eligibility reporting process.</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Extraction and file generation complete successfully.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>US_2045</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Outbound Member Eligibility Reporting</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>TS_016: Verify end-to-end processing from extraction through file creation and status update</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Validate the generated file contents and file name.</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Output contains only eligible valid records and file name matches the required naming convention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>US_2045</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Outbound Member Eligibility Reporting</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>TS_016: Verify end-to-end processing from extraction through file creation and status update</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Review the linked local staging record after successful file creation.</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Local staging record status is updated from Ready to Processed immediately after successful file creation.</t>
+          <t>The processed Ready record changes to Processed; unrelated records in other statuses remain unchanged unless independently processed by design.</t>
         </is>
       </c>
     </row>
